--- a/template/12.4/净值.xlsx
+++ b/template/12.4/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21611" windowHeight="8784" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27990" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00000_ "/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy\/mm\/dd"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy\/mm\/dd"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -632,7 +633,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -644,7 +645,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -653,11 +655,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1036,11 +1039,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E160"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.3333333333333" customWidth="1" style="6" min="2" max="2"/>
-    <col width="15.3333333333333" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.3333333333333" customWidth="1" style="7" min="2" max="2"/>
+    <col width="15.3333333333333" customWidth="1" style="8" min="3" max="3"/>
     <col width="15.3333333333333" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
@@ -1050,7 +1053,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -1072,13 +1075,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="9" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1093,7 +1096,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -1116,7 +1119,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -1139,7 +1142,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -1162,7 +1165,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -1185,7 +1188,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -1208,7 +1211,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -1231,7 +1234,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -1254,7 +1257,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -1277,7 +1280,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -1300,7 +1303,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -1323,7 +1326,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -1346,7 +1349,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -1369,7 +1372,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -1392,7 +1395,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -1415,7 +1418,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -1438,7 +1441,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -1461,7 +1464,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -1484,7 +1487,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -1507,7 +1510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -1530,7 +1533,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -1553,7 +1556,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -1576,7 +1579,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -1599,7 +1602,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -1622,7 +1625,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -1645,7 +1648,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -1668,7 +1671,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -1691,7 +1694,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -1714,7 +1717,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -1737,7 +1740,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -1760,7 +1763,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -1783,7 +1786,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -1806,7 +1809,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -1829,7 +1832,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -1852,7 +1855,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -1875,7 +1878,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -1898,7 +1901,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -1921,7 +1924,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -1944,7 +1947,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -1967,7 +1970,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -1990,7 +1993,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -2013,7 +2016,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -2036,7 +2039,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -2059,7 +2062,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -2082,7 +2085,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -2105,7 +2108,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -2128,7 +2131,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -2151,7 +2154,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -2174,7 +2177,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -2197,7 +2200,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -2220,7 +2223,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -2243,7 +2246,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -2266,7 +2269,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -2289,7 +2292,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -2312,7 +2315,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -2335,7 +2338,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -2358,7 +2361,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -2381,7 +2384,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -2404,7 +2407,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -2427,7 +2430,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -2450,7 +2453,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -2473,7 +2476,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -2496,7 +2499,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -2519,7 +2522,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -2542,7 +2545,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -2565,7 +2568,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -2588,7 +2591,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -2611,7 +2614,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -2634,7 +2637,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -2657,7 +2660,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -2680,7 +2683,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -2703,7 +2706,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -2726,7 +2729,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -2749,7 +2752,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -2772,7 +2775,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -2795,7 +2798,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -2818,7 +2821,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -2841,7 +2844,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -2864,7 +2867,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -2887,7 +2890,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -2910,7 +2913,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -2933,7 +2936,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -2956,7 +2959,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -2979,7 +2982,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -3002,7 +3005,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -3025,7 +3028,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -3048,7 +3051,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -3071,7 +3074,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -3094,7 +3097,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -3117,7 +3120,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -3140,7 +3143,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -3163,7 +3166,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3186,7 +3189,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
@@ -3209,7 +3212,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>2025/07/09</t>
         </is>
@@ -3232,7 +3235,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
@@ -3255,7 +3258,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>2025/07/11</t>
         </is>
@@ -3278,7 +3281,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>2025/07/14</t>
         </is>
@@ -3301,7 +3304,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
@@ -3324,7 +3327,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>2025/07/16</t>
         </is>
@@ -3347,7 +3350,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>2025/07/17</t>
         </is>
@@ -3370,7 +3373,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
@@ -3393,7 +3396,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>2025/07/21</t>
         </is>
@@ -3416,7 +3419,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>2025/07/22</t>
         </is>
@@ -3439,7 +3442,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>2025/07/23</t>
         </is>
@@ -3462,7 +3465,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
@@ -3485,7 +3488,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>2025/07/25</t>
         </is>
@@ -3508,7 +3511,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
@@ -3531,7 +3534,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
@@ -3554,7 +3557,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>2025/07/30</t>
         </is>
@@ -3577,7 +3580,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>2025/07/31</t>
         </is>
@@ -3600,7 +3603,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>2025/08/01</t>
         </is>
@@ -3623,7 +3626,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>2025/08/04</t>
         </is>
@@ -3646,7 +3649,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>2025/08/05</t>
         </is>
@@ -3669,7 +3672,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>2025/08/06</t>
         </is>
@@ -3692,7 +3695,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
@@ -3715,7 +3718,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
@@ -3738,7 +3741,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>2025/08/11</t>
         </is>
@@ -3761,7 +3764,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>2025/08/12</t>
         </is>
@@ -3784,7 +3787,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
@@ -3807,7 +3810,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>2025/08/14</t>
         </is>
@@ -3830,7 +3833,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>2025/08/15</t>
         </is>
@@ -3853,7 +3856,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
@@ -3876,7 +3879,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>2025/08/19</t>
         </is>
@@ -3899,7 +3902,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
@@ -3922,7 +3925,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>2025/08/21</t>
         </is>
@@ -3945,7 +3948,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
@@ -3968,7 +3971,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
@@ -3991,7 +3994,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>2025/08/26</t>
         </is>
@@ -4014,7 +4017,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
@@ -4037,7 +4040,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>2025/08/28</t>
         </is>
@@ -4060,7 +4063,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
@@ -4083,7 +4086,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
@@ -4106,7 +4109,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>2025/09/02</t>
         </is>
@@ -4129,7 +4132,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
@@ -4152,7 +4155,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>2025/09/04</t>
         </is>
@@ -4175,7 +4178,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>2025/09/05</t>
         </is>
@@ -4198,7 +4201,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="inlineStr">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>2025/09/08</t>
         </is>
@@ -4221,7 +4224,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>2025/09/09</t>
         </is>
@@ -4244,7 +4247,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>2025/09/10</t>
         </is>
@@ -4267,7 +4270,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
@@ -4290,7 +4293,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="inlineStr">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>2025/09/12</t>
         </is>
@@ -4313,7 +4316,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
+      <c r="A143" s="10" t="inlineStr">
         <is>
           <t>2025/09/15</t>
         </is>
@@ -4336,7 +4339,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="inlineStr">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>2025/09/16</t>
         </is>
@@ -4359,7 +4362,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
@@ -4382,7 +4385,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
@@ -4405,7 +4408,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="inlineStr">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>2025/09/19</t>
         </is>
@@ -4428,7 +4431,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
+      <c r="A148" s="10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
@@ -4451,7 +4454,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="inlineStr">
+      <c r="A149" s="10" t="inlineStr">
         <is>
           <t>2025/09/23</t>
         </is>
@@ -4474,7 +4477,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>2025/09/25</t>
         </is>
@@ -4497,7 +4500,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>2025/09/26</t>
         </is>
@@ -4520,7 +4523,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="inlineStr">
+      <c r="A152" s="10" t="inlineStr">
         <is>
           <t>2025/09/29</t>
         </is>
@@ -4543,7 +4546,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="A153" s="10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
@@ -4566,7 +4569,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="inlineStr">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t>2025/10/09</t>
         </is>
@@ -4589,7 +4592,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="10" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t>2025/10/10</t>
         </is>
@@ -4612,7 +4615,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>2025/10/13</t>
         </is>
@@ -4635,7 +4638,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="inlineStr">
+      <c r="A157" s="11" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
@@ -4658,7 +4661,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
@@ -4681,7 +4684,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="10" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>2025/10/16</t>
         </is>
@@ -4704,7 +4707,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="11" t="inlineStr">
         <is>
           <t>2025/10/17</t>
         </is>
@@ -4729,12 +4732,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E151"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="12.8888888888889" customWidth="1" style="6" min="2" max="2"/>
-    <col width="12.8888888888889" customWidth="1" style="7" min="3" max="3"/>
-    <col width="12.8888888888889" customWidth="1" style="1" min="4" max="5"/>
+    <col width="12.8916666666667" customWidth="1" style="7" min="2" max="2"/>
+    <col width="12.8916666666667" customWidth="1" style="8" min="3" max="3"/>
+    <col width="12.8916666666667" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4765,13 +4768,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="9" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -4786,7 +4789,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -4809,7 +4812,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -4832,7 +4835,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -4855,7 +4858,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -4878,7 +4881,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -4901,7 +4904,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -4924,7 +4927,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -4947,7 +4950,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -4970,7 +4973,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -4993,7 +4996,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -5016,7 +5019,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -5039,7 +5042,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -5062,7 +5065,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -5085,7 +5088,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -5108,7 +5111,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -5131,7 +5134,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -5154,7 +5157,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -5177,7 +5180,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -5200,7 +5203,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -5223,7 +5226,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -5246,7 +5249,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -5269,7 +5272,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -5292,7 +5295,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -5315,7 +5318,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -5338,7 +5341,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -5361,7 +5364,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -5384,7 +5387,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -5407,7 +5410,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -5430,7 +5433,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -5453,7 +5456,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -5476,7 +5479,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -5499,7 +5502,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -5522,7 +5525,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -5545,7 +5548,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -5568,7 +5571,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -5591,7 +5594,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -5614,7 +5617,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -5637,7 +5640,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -5660,7 +5663,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -5683,7 +5686,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -5706,7 +5709,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -5729,7 +5732,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -5752,7 +5755,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -5775,7 +5778,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -5798,7 +5801,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -5821,7 +5824,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -5844,7 +5847,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -5867,7 +5870,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -5890,7 +5893,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -5913,7 +5916,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -5936,7 +5939,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -5959,7 +5962,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -5982,7 +5985,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -6005,7 +6008,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -6028,7 +6031,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -6051,7 +6054,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -6074,7 +6077,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -6097,7 +6100,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -6120,7 +6123,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -6143,7 +6146,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -6166,7 +6169,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -6189,7 +6192,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -6212,7 +6215,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -6235,7 +6238,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -6258,7 +6261,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -6281,7 +6284,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -6304,7 +6307,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -6327,7 +6330,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -6350,7 +6353,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -6373,7 +6376,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -6396,7 +6399,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -6419,7 +6422,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -6442,7 +6445,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -6465,7 +6468,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -6488,7 +6491,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -6511,7 +6514,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -6534,7 +6537,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -6557,7 +6560,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -6580,7 +6583,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -6603,7 +6606,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -6626,7 +6629,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -6649,7 +6652,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -6672,7 +6675,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -6695,7 +6698,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -6718,7 +6721,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -6741,7 +6744,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -6764,7 +6767,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -6787,7 +6790,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -6810,7 +6813,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -6833,7 +6836,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -6856,7 +6859,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -6879,7 +6882,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
@@ -6902,7 +6905,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>2025/07/09</t>
         </is>
@@ -6925,7 +6928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
@@ -6948,7 +6951,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>2025/07/11</t>
         </is>
@@ -6971,7 +6974,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>2025/07/14</t>
         </is>
@@ -6994,7 +6997,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
@@ -7017,7 +7020,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>2025/07/16</t>
         </is>
@@ -7040,7 +7043,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>2025/07/17</t>
         </is>
@@ -7063,7 +7066,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
@@ -7086,7 +7089,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>2025/07/21</t>
         </is>
@@ -7109,7 +7112,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>2025/07/22</t>
         </is>
@@ -7132,7 +7135,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>2025/07/23</t>
         </is>
@@ -7155,7 +7158,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
@@ -7178,7 +7181,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>2025/07/25</t>
         </is>
@@ -7201,7 +7204,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
@@ -7224,7 +7227,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
@@ -7247,7 +7250,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>2025/07/30</t>
         </is>
@@ -7270,7 +7273,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>2025/07/31</t>
         </is>
@@ -7293,7 +7296,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>2025/08/01</t>
         </is>
@@ -7316,7 +7319,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>2025/08/04</t>
         </is>
@@ -7339,7 +7342,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>2025/08/05</t>
         </is>
@@ -7362,7 +7365,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>2025/08/06</t>
         </is>
@@ -7385,7 +7388,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
@@ -7408,7 +7411,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
@@ -7431,7 +7434,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>2025/08/11</t>
         </is>
@@ -7454,7 +7457,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>2025/08/12</t>
         </is>
@@ -7477,7 +7480,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
@@ -7500,7 +7503,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>2025/08/14</t>
         </is>
@@ -7523,7 +7526,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>2025/08/15</t>
         </is>
@@ -7546,7 +7549,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
@@ -7569,7 +7572,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>2025/08/19</t>
         </is>
@@ -7592,7 +7595,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
@@ -7615,7 +7618,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>2025/08/21</t>
         </is>
@@ -7638,7 +7641,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
@@ -7661,7 +7664,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
@@ -7684,7 +7687,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>2025/08/26</t>
         </is>
@@ -7707,7 +7710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
@@ -7730,7 +7733,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>2025/08/28</t>
         </is>
@@ -7753,7 +7756,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
@@ -7776,7 +7779,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
@@ -7799,7 +7802,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>2025/09/02</t>
         </is>
@@ -7822,7 +7825,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
@@ -7845,7 +7848,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>2025/09/04</t>
         </is>
@@ -7868,7 +7871,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>2025/09/05</t>
         </is>
@@ -7891,7 +7894,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="inlineStr">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>2025/09/08</t>
         </is>
@@ -7914,7 +7917,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>2025/09/09</t>
         </is>
@@ -7937,7 +7940,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>2025/09/10</t>
         </is>
@@ -7960,7 +7963,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
@@ -7983,7 +7986,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="inlineStr">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>2025/09/12</t>
         </is>
@@ -8006,7 +8009,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
+      <c r="A143" s="10" t="inlineStr">
         <is>
           <t>2025/09/15</t>
         </is>
@@ -8029,7 +8032,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="inlineStr">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>2025/09/16</t>
         </is>
@@ -8052,7 +8055,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
@@ -8075,7 +8078,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
@@ -8098,7 +8101,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="inlineStr">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>2025/09/19</t>
         </is>
@@ -8121,7 +8124,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
+      <c r="A148" s="10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
@@ -8144,7 +8147,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="inlineStr">
+      <c r="A149" s="10" t="inlineStr">
         <is>
           <t>2025/09/23</t>
         </is>
@@ -8167,7 +8170,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>2025/09/25</t>
         </is>
@@ -8180,7 +8183,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>2025/09/26</t>
         </is>
@@ -8204,13 +8207,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E181"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="14.1111111111111" customWidth="1" style="6" min="2" max="2"/>
-    <col width="14.1111111111111" customWidth="1" style="7" min="3" max="3"/>
-    <col width="14.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="14.1083333333333" customWidth="1" style="7" min="2" max="2"/>
+    <col width="14.1083333333333" customWidth="1" style="8" min="3" max="3"/>
+    <col width="14.1083333333333" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8241,15 +8244,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -8264,15 +8267,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -8287,7 +8290,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -8310,7 +8313,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -8333,7 +8336,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -8356,7 +8359,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -8379,7 +8382,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -8402,7 +8405,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -8425,7 +8428,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -8448,7 +8451,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -8471,7 +8474,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -8494,7 +8497,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -8517,7 +8520,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -8540,7 +8543,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -8563,7 +8566,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -8586,7 +8589,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -8609,7 +8612,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -8632,7 +8635,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -8655,7 +8658,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -8678,7 +8681,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -8701,7 +8704,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -8724,7 +8727,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -8747,7 +8750,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -8770,7 +8773,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -8793,7 +8796,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -8816,7 +8819,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -8839,7 +8842,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -8862,7 +8865,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -8885,7 +8888,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -8908,7 +8911,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -8931,7 +8934,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -8954,7 +8957,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -8977,7 +8980,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -9000,7 +9003,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -9023,7 +9026,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -9046,7 +9049,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -9069,7 +9072,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -9092,7 +9095,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -9115,7 +9118,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -9138,7 +9141,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -9161,7 +9164,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -9184,7 +9187,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -9207,7 +9210,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -9230,7 +9233,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -9253,7 +9256,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -9276,7 +9279,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -9299,7 +9302,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -9322,7 +9325,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -9345,7 +9348,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -9368,7 +9371,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -9391,7 +9394,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -9414,7 +9417,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -9437,7 +9440,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -9460,7 +9463,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -9483,7 +9486,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -9506,7 +9509,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -9529,7 +9532,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -9552,7 +9555,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -9575,7 +9578,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -9598,7 +9601,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -9621,7 +9624,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -9644,7 +9647,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -9667,7 +9670,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -9690,7 +9693,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -9713,7 +9716,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -9736,7 +9739,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -9759,7 +9762,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -9782,7 +9785,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -9805,7 +9808,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -9828,7 +9831,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -9851,7 +9854,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -9874,7 +9877,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -9897,7 +9900,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -9920,7 +9923,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -9943,7 +9946,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9966,7 +9969,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
@@ -9989,7 +9992,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>2025/07/09</t>
         </is>
@@ -10012,7 +10015,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
@@ -10035,7 +10038,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>2025/07/11</t>
         </is>
@@ -10058,7 +10061,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>2025/07/14</t>
         </is>
@@ -10081,7 +10084,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
@@ -10104,7 +10107,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>2025/07/16</t>
         </is>
@@ -10127,7 +10130,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>2025/07/17</t>
         </is>
@@ -10150,7 +10153,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
@@ -10173,7 +10176,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>2025/07/21</t>
         </is>
@@ -10196,7 +10199,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>2025/07/22</t>
         </is>
@@ -10219,7 +10222,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>2025/07/23</t>
         </is>
@@ -10242,7 +10245,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
@@ -10265,7 +10268,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>2025/07/25</t>
         </is>
@@ -10288,7 +10291,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
@@ -10311,7 +10314,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
@@ -10334,7 +10337,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>2025/07/30</t>
         </is>
@@ -10357,7 +10360,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>2025/07/31</t>
         </is>
@@ -10380,7 +10383,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>2025/08/01</t>
         </is>
@@ -10403,7 +10406,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>2025/08/04</t>
         </is>
@@ -10426,7 +10429,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>2025/08/05</t>
         </is>
@@ -10449,7 +10452,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>2025/08/06</t>
         </is>
@@ -10472,7 +10475,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
@@ -10495,7 +10498,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
@@ -10518,7 +10521,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>2025/08/11</t>
         </is>
@@ -10541,7 +10544,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>2025/08/12</t>
         </is>
@@ -10564,7 +10567,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
@@ -10587,7 +10590,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>2025/08/14</t>
         </is>
@@ -10610,7 +10613,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>2025/08/15</t>
         </is>
@@ -10633,7 +10636,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
@@ -10656,7 +10659,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>2025/08/19</t>
         </is>
@@ -10679,7 +10682,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
@@ -10702,7 +10705,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>2025/08/21</t>
         </is>
@@ -10725,7 +10728,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
@@ -10748,7 +10751,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
@@ -10771,7 +10774,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>2025/08/26</t>
         </is>
@@ -10794,7 +10797,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
@@ -10817,7 +10820,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>2025/08/28</t>
         </is>
@@ -10840,7 +10843,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
@@ -10863,7 +10866,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
@@ -10886,7 +10889,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>2025/09/02</t>
         </is>
@@ -10909,7 +10912,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
@@ -10932,7 +10935,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>2025/09/04</t>
         </is>
@@ -10955,7 +10958,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>2025/09/05</t>
         </is>
@@ -10978,7 +10981,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>2025/09/08</t>
         </is>
@@ -11001,7 +11004,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>2025/09/09</t>
         </is>
@@ -11024,7 +11027,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>2025/09/10</t>
         </is>
@@ -11047,7 +11050,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
@@ -11070,7 +11073,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>2025/09/12</t>
         </is>
@@ -11093,7 +11096,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>2025/09/15</t>
         </is>
@@ -11116,7 +11119,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>2025/09/16</t>
         </is>
@@ -11139,7 +11142,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
@@ -11162,7 +11165,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
@@ -11185,7 +11188,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>2025/09/19</t>
         </is>
@@ -11208,7 +11211,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
@@ -11231,7 +11234,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>2025/09/23</t>
         </is>
@@ -11254,7 +11257,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
@@ -11277,7 +11280,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>2025/09/25</t>
         </is>
@@ -11300,7 +11303,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>2025/09/26</t>
         </is>
@@ -11323,7 +11326,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>2025/09/29</t>
         </is>
@@ -11346,7 +11349,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
@@ -11369,7 +11372,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="10" t="inlineStr">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t>2025/10/09</t>
         </is>
@@ -11392,7 +11395,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="A139" s="11" t="inlineStr">
         <is>
           <t>2025/10/10</t>
         </is>
@@ -11415,7 +11418,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="10" t="inlineStr">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>2025/10/13</t>
         </is>
@@ -11438,7 +11441,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="10" t="inlineStr">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
@@ -11461,7 +11464,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="10" t="inlineStr">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
@@ -11484,7 +11487,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="10" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>2025/10/16</t>
         </is>
@@ -11507,7 +11510,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>2025/10/17</t>
         </is>
@@ -11530,7 +11533,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="10" t="inlineStr">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
@@ -11553,7 +11556,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="10" t="inlineStr">
+      <c r="A146" s="11" t="inlineStr">
         <is>
           <t>2025/10/21</t>
         </is>
@@ -11576,7 +11579,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="10" t="inlineStr">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t>2025/10/22</t>
         </is>
@@ -11599,7 +11602,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="10" t="inlineStr">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>2025/10/23</t>
         </is>
@@ -11622,7 +11625,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="10" t="inlineStr">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>2025/10/24</t>
         </is>
@@ -11645,7 +11648,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="10" t="inlineStr">
+      <c r="A150" s="11" t="inlineStr">
         <is>
           <t>2025/10/27</t>
         </is>
@@ -11668,7 +11671,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="10" t="inlineStr">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>2025/10/28</t>
         </is>
@@ -11691,7 +11694,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="inlineStr">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
@@ -11714,7 +11717,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="10" t="inlineStr">
+      <c r="A153" s="11" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
@@ -11737,7 +11740,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="inlineStr">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t>2025/10/31</t>
         </is>
@@ -11760,7 +11763,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="10" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t>2025/11/03</t>
         </is>
@@ -11783,7 +11786,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
@@ -11806,7 +11809,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="inlineStr">
+      <c r="A157" s="11" t="inlineStr">
         <is>
           <t>2025/11/05</t>
         </is>
@@ -11829,7 +11832,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>2025/11/06</t>
         </is>
@@ -11852,7 +11855,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="10" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>2025/11/07</t>
         </is>
@@ -11875,7 +11878,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="11" t="inlineStr">
         <is>
           <t>2025/11/10</t>
         </is>
@@ -11898,7 +11901,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="10" t="inlineStr">
+      <c r="A161" s="11" t="inlineStr">
         <is>
           <t>2025/11/11</t>
         </is>
@@ -11921,7 +11924,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="10" t="inlineStr">
+      <c r="A162" s="11" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
@@ -11944,7 +11947,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="10" t="inlineStr">
+      <c r="A163" s="11" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
@@ -11967,7 +11970,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
+      <c r="A164" s="11" t="inlineStr">
         <is>
           <t>2025/11/14</t>
         </is>
@@ -11990,7 +11993,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="10" t="inlineStr">
+      <c r="A165" s="11" t="inlineStr">
         <is>
           <t>2025/11/17</t>
         </is>
@@ -12013,7 +12016,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="inlineStr">
+      <c r="A166" s="11" t="inlineStr">
         <is>
           <t>2025/11/18</t>
         </is>
@@ -12036,7 +12039,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="inlineStr">
+      <c r="A167" s="11" t="inlineStr">
         <is>
           <t>2025/11/19</t>
         </is>
@@ -12059,7 +12062,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="inlineStr">
+      <c r="A168" s="11" t="inlineStr">
         <is>
           <t>2025/11/20</t>
         </is>
@@ -12082,7 +12085,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="inlineStr">
+      <c r="A169" s="11" t="inlineStr">
         <is>
           <t>2025/11/21</t>
         </is>
@@ -12105,7 +12108,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="10" t="inlineStr">
+      <c r="A170" s="11" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
@@ -12128,7 +12131,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="10" t="inlineStr">
+      <c r="A171" s="11" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
@@ -12151,7 +12154,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="10" t="inlineStr">
+      <c r="A172" s="11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
@@ -12174,7 +12177,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="10" t="inlineStr">
+      <c r="A173" s="11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
@@ -12197,7 +12200,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="10" t="inlineStr">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
@@ -12220,7 +12223,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="10" t="inlineStr">
+      <c r="A175" s="11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
@@ -12243,7 +12246,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="10" t="inlineStr">
+      <c r="A176" s="11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
@@ -12266,7 +12269,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="10" t="inlineStr">
+      <c r="A177" s="11" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
@@ -12289,23 +12292,92 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="10" t="inlineStr">
+      <c r="A178" s="12" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="0" t="n">
         <v>1.00495</v>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="0" t="inlineStr">
         <is>
           <t>-1.8687%</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="0" t="n">
         <v>0.99777</v>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t>-2.5481%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>1.00495</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>-1.8687%</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>0.99777</v>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t>-2.5481%</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="n">
+        <v>1.00495</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>-1.8687%</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="n">
+        <v>0.99777</v>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t>-2.5481%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1.00495</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>-1.8687%</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.99777</v>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>-2.5481%</t>
         </is>
@@ -12323,13 +12395,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E181"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="6" min="2" max="2"/>
-    <col width="15.1111111111111" customWidth="1" style="7" min="3" max="3"/>
-    <col width="15.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="15.1083333333333" customWidth="1" style="7" min="2" max="2"/>
+    <col width="15.1083333333333" customWidth="1" style="8" min="3" max="3"/>
+    <col width="15.1083333333333" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12360,15 +12432,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -12383,15 +12455,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -12406,7 +12478,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -12429,7 +12501,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -12452,7 +12524,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -12475,7 +12547,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -12498,7 +12570,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -12521,7 +12593,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -12544,7 +12616,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -12567,7 +12639,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -12590,7 +12662,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -12613,7 +12685,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -12636,7 +12708,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -12659,7 +12731,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -12682,7 +12754,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -12705,7 +12777,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -12728,7 +12800,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -12751,7 +12823,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -12774,7 +12846,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -12797,7 +12869,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -12820,7 +12892,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -12843,7 +12915,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -12866,7 +12938,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -12889,7 +12961,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -12912,7 +12984,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -12935,7 +13007,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -12958,7 +13030,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -12981,7 +13053,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -13004,7 +13076,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -13027,7 +13099,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -13050,7 +13122,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -13073,7 +13145,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -13096,7 +13168,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -13119,7 +13191,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -13142,7 +13214,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -13165,7 +13237,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -13188,7 +13260,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -13211,7 +13283,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -13234,7 +13306,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -13257,7 +13329,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -13280,7 +13352,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -13303,7 +13375,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -13326,7 +13398,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -13349,7 +13421,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -13372,7 +13444,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -13395,7 +13467,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -13418,7 +13490,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -13441,7 +13513,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -13464,7 +13536,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -13487,7 +13559,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -13510,7 +13582,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -13533,7 +13605,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -13556,7 +13628,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -13579,7 +13651,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -13602,7 +13674,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -13625,7 +13697,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -13648,7 +13720,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -13671,7 +13743,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -13694,7 +13766,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -13717,7 +13789,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -13740,7 +13812,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -13763,7 +13835,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -13786,7 +13858,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -13809,7 +13881,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -13832,7 +13904,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -13855,7 +13927,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -13878,7 +13950,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -13901,7 +13973,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -13924,7 +13996,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -13947,7 +14019,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -13970,7 +14042,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -13993,7 +14065,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -14016,7 +14088,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -14039,7 +14111,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -14062,7 +14134,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -14085,7 +14157,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
@@ -14108,7 +14180,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>2025/07/09</t>
         </is>
@@ -14131,7 +14203,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
@@ -14154,7 +14226,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>2025/07/11</t>
         </is>
@@ -14177,7 +14249,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>2025/07/14</t>
         </is>
@@ -14200,7 +14272,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
@@ -14223,7 +14295,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>2025/07/16</t>
         </is>
@@ -14246,7 +14318,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>2025/07/17</t>
         </is>
@@ -14269,7 +14341,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
@@ -14292,7 +14364,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>2025/07/21</t>
         </is>
@@ -14315,7 +14387,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>2025/07/22</t>
         </is>
@@ -14338,7 +14410,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>2025/07/23</t>
         </is>
@@ -14361,7 +14433,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
@@ -14384,7 +14456,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>2025/07/25</t>
         </is>
@@ -14407,7 +14479,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
@@ -14430,7 +14502,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
@@ -14453,7 +14525,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>2025/07/30</t>
         </is>
@@ -14476,7 +14548,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>2025/07/31</t>
         </is>
@@ -14499,7 +14571,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>2025/08/01</t>
         </is>
@@ -14522,7 +14594,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>2025/08/04</t>
         </is>
@@ -14545,7 +14617,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>2025/08/05</t>
         </is>
@@ -14568,7 +14640,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>2025/08/06</t>
         </is>
@@ -14591,7 +14663,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
@@ -14614,7 +14686,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
@@ -14637,7 +14709,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>2025/08/11</t>
         </is>
@@ -14660,7 +14732,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>2025/08/12</t>
         </is>
@@ -14683,7 +14755,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
@@ -14706,7 +14778,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>2025/08/14</t>
         </is>
@@ -14729,7 +14801,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>2025/08/15</t>
         </is>
@@ -14752,7 +14824,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
@@ -14775,7 +14847,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>2025/08/19</t>
         </is>
@@ -14798,7 +14870,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
@@ -14821,7 +14893,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>2025/08/21</t>
         </is>
@@ -14844,7 +14916,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
@@ -14867,7 +14939,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
@@ -14890,7 +14962,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>2025/08/26</t>
         </is>
@@ -14913,7 +14985,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
@@ -14936,7 +15008,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>2025/08/28</t>
         </is>
@@ -14959,7 +15031,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
@@ -14982,7 +15054,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
@@ -15005,7 +15077,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>2025/09/02</t>
         </is>
@@ -15028,7 +15100,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
@@ -15051,7 +15123,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>2025/09/04</t>
         </is>
@@ -15074,7 +15146,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>2025/09/05</t>
         </is>
@@ -15097,7 +15169,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>2025/09/08</t>
         </is>
@@ -15120,7 +15192,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>2025/09/09</t>
         </is>
@@ -15143,7 +15215,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>2025/09/10</t>
         </is>
@@ -15166,7 +15238,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
@@ -15189,7 +15261,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>2025/09/12</t>
         </is>
@@ -15212,7 +15284,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>2025/09/15</t>
         </is>
@@ -15235,7 +15307,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>2025/09/16</t>
         </is>
@@ -15258,7 +15330,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
@@ -15281,7 +15353,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
@@ -15304,7 +15376,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>2025/09/19</t>
         </is>
@@ -15327,7 +15399,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
@@ -15350,7 +15422,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>2025/09/23</t>
         </is>
@@ -15373,7 +15445,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
@@ -15396,7 +15468,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>2025/09/25</t>
         </is>
@@ -15419,7 +15491,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>2025/09/26</t>
         </is>
@@ -15442,7 +15514,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>2025/09/29</t>
         </is>
@@ -15465,7 +15537,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
@@ -15488,7 +15560,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="10" t="inlineStr">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t>2025/10/09</t>
         </is>
@@ -15511,7 +15583,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="A139" s="11" t="inlineStr">
         <is>
           <t>2025/10/10</t>
         </is>
@@ -15534,7 +15606,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="10" t="inlineStr">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>2025/10/13</t>
         </is>
@@ -15557,7 +15629,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="10" t="inlineStr">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
@@ -15580,7 +15652,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="10" t="inlineStr">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
@@ -15603,7 +15675,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="10" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>2025/10/16</t>
         </is>
@@ -15626,7 +15698,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>2025/10/17</t>
         </is>
@@ -15649,7 +15721,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="10" t="inlineStr">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
@@ -15672,7 +15744,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="10" t="inlineStr">
+      <c r="A146" s="11" t="inlineStr">
         <is>
           <t>2025/10/21</t>
         </is>
@@ -15695,7 +15767,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="10" t="inlineStr">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t>2025/10/22</t>
         </is>
@@ -15718,7 +15790,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="10" t="inlineStr">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>2025/10/23</t>
         </is>
@@ -15741,7 +15813,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="10" t="inlineStr">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>2025/10/24</t>
         </is>
@@ -15764,7 +15836,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="10" t="inlineStr">
+      <c r="A150" s="11" t="inlineStr">
         <is>
           <t>2025/10/27</t>
         </is>
@@ -15787,7 +15859,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="10" t="inlineStr">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>2025/10/28</t>
         </is>
@@ -15810,7 +15882,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="inlineStr">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
@@ -15833,7 +15905,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="10" t="inlineStr">
+      <c r="A153" s="11" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
@@ -15856,7 +15928,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="inlineStr">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t>2025/10/31</t>
         </is>
@@ -15879,7 +15951,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="10" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t>2025/11/03</t>
         </is>
@@ -15902,7 +15974,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
@@ -15925,7 +15997,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="inlineStr">
+      <c r="A157" s="11" t="inlineStr">
         <is>
           <t>2025/11/05</t>
         </is>
@@ -15948,7 +16020,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>2025/11/06</t>
         </is>
@@ -15971,7 +16043,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="10" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>2025/11/07</t>
         </is>
@@ -15994,7 +16066,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="11" t="inlineStr">
         <is>
           <t>2025/11/10</t>
         </is>
@@ -16017,7 +16089,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="10" t="inlineStr">
+      <c r="A161" s="11" t="inlineStr">
         <is>
           <t>2025/11/11</t>
         </is>
@@ -16040,7 +16112,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="10" t="inlineStr">
+      <c r="A162" s="11" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
@@ -16063,7 +16135,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="10" t="inlineStr">
+      <c r="A163" s="11" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
@@ -16086,7 +16158,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
+      <c r="A164" s="11" t="inlineStr">
         <is>
           <t>2025/11/14</t>
         </is>
@@ -16109,7 +16181,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="10" t="inlineStr">
+      <c r="A165" s="11" t="inlineStr">
         <is>
           <t>2025/11/17</t>
         </is>
@@ -16132,7 +16204,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="inlineStr">
+      <c r="A166" s="11" t="inlineStr">
         <is>
           <t>2025/11/18</t>
         </is>
@@ -16155,7 +16227,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="inlineStr">
+      <c r="A167" s="11" t="inlineStr">
         <is>
           <t>2025/11/19</t>
         </is>
@@ -16178,7 +16250,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="inlineStr">
+      <c r="A168" s="11" t="inlineStr">
         <is>
           <t>2025/11/20</t>
         </is>
@@ -16201,7 +16273,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="inlineStr">
+      <c r="A169" s="11" t="inlineStr">
         <is>
           <t>2025/11/21</t>
         </is>
@@ -16224,7 +16296,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="10" t="inlineStr">
+      <c r="A170" s="11" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
@@ -16247,7 +16319,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="10" t="inlineStr">
+      <c r="A171" s="11" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
@@ -16270,7 +16342,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="10" t="inlineStr">
+      <c r="A172" s="11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
@@ -16293,7 +16365,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="10" t="inlineStr">
+      <c r="A173" s="11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
@@ -16316,7 +16388,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="10" t="inlineStr">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
@@ -16339,7 +16411,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="10" t="inlineStr">
+      <c r="A175" s="11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
@@ -16362,7 +16434,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="10" t="inlineStr">
+      <c r="A176" s="11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
@@ -16385,7 +16457,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="10" t="inlineStr">
+      <c r="A177" s="11" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
@@ -16408,23 +16480,92 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="10" t="inlineStr">
+      <c r="A178" s="12" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="0" t="n">
         <v>1.00526</v>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="0" t="inlineStr">
         <is>
           <t>-2.2436%</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="0" t="n">
         <v>0.99808</v>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t>-2.9203%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>1.00526</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>-2.2436%</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>0.99808</v>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t>-2.9203%</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="n">
+        <v>1.00526</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>-2.2436%</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="n">
+        <v>0.99808</v>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t>-2.9203%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1.00526</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>-2.2436%</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.99808</v>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>-2.9203%</t>
         </is>
@@ -16442,13 +16583,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="6" min="2" max="2"/>
-    <col width="15.1111111111111" customWidth="1" style="7" min="3" max="3"/>
-    <col width="15.1111111111111" customWidth="1" style="1" min="4" max="5"/>
+    <col width="15.1083333333333" customWidth="1" style="7" min="2" max="2"/>
+    <col width="15.1083333333333" customWidth="1" style="8" min="3" max="3"/>
+    <col width="15.1083333333333" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16479,7 +16620,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -16487,7 +16628,7 @@
       <c r="B2" s="0" t="n">
         <v>0.99988</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>-0.0124%</t>
         </is>
@@ -16502,7 +16643,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -16525,7 +16666,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -16548,7 +16689,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -16571,7 +16712,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -16594,7 +16735,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -16617,7 +16758,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -16640,7 +16781,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -16663,7 +16804,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -16686,7 +16827,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -16709,7 +16850,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -16732,7 +16873,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -16755,7 +16896,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -16778,7 +16919,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -16801,7 +16942,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -16824,7 +16965,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -16847,7 +16988,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -16870,7 +17011,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -16893,7 +17034,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -16916,7 +17057,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -16939,7 +17080,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -16962,7 +17103,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
@@ -16985,7 +17126,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2025/07/09</t>
         </is>
@@ -17008,7 +17149,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
@@ -17031,7 +17172,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2025/07/11</t>
         </is>
@@ -17054,7 +17195,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2025/07/14</t>
         </is>
@@ -17077,7 +17218,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
@@ -17100,7 +17241,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2025/07/16</t>
         </is>
@@ -17123,7 +17264,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025/07/17</t>
         </is>
@@ -17146,7 +17287,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
@@ -17169,7 +17310,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2025/07/21</t>
         </is>
@@ -17192,7 +17333,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2025/07/22</t>
         </is>
@@ -17215,7 +17356,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2025/07/23</t>
         </is>
@@ -17238,7 +17379,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
@@ -17261,7 +17402,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2025/07/25</t>
         </is>
@@ -17284,7 +17425,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
@@ -17307,7 +17448,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
@@ -17330,7 +17471,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2025/07/30</t>
         </is>
@@ -17353,7 +17494,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2025/07/31</t>
         </is>
@@ -17376,7 +17517,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2025/08/01</t>
         </is>
@@ -17399,7 +17540,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2025/08/04</t>
         </is>
@@ -17422,7 +17563,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2025/08/05</t>
         </is>
@@ -17445,7 +17586,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2025/08/06</t>
         </is>
@@ -17468,7 +17609,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
@@ -17491,7 +17632,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
@@ -17514,7 +17655,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2025/08/11</t>
         </is>
@@ -17537,7 +17678,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2025/08/12</t>
         </is>
@@ -17560,7 +17701,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
@@ -17583,7 +17724,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2025/08/14</t>
         </is>
@@ -17606,7 +17747,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2025/08/15</t>
         </is>
@@ -17629,7 +17770,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
@@ -17652,7 +17793,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2025/08/19</t>
         </is>
@@ -17675,7 +17816,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
@@ -17698,7 +17839,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2025/08/21</t>
         </is>
@@ -17721,7 +17862,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
@@ -17744,7 +17885,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
@@ -17767,7 +17908,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2025/08/26</t>
         </is>
@@ -17790,7 +17931,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
@@ -17813,7 +17954,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>2025/08/28</t>
         </is>
@@ -17836,7 +17977,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
@@ -17859,7 +18000,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
@@ -17882,7 +18023,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>2025/09/02</t>
         </is>
@@ -17905,7 +18046,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
@@ -17928,7 +18069,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>2025/09/04</t>
         </is>
@@ -17951,7 +18092,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>2025/09/05</t>
         </is>
@@ -17974,7 +18115,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2025/09/08</t>
         </is>
@@ -17997,7 +18138,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>2025/09/09</t>
         </is>
@@ -18020,7 +18161,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>2025/09/10</t>
         </is>
@@ -18043,7 +18184,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
@@ -18066,7 +18207,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>2025/09/12</t>
         </is>
@@ -18089,7 +18230,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>2025/09/15</t>
         </is>
@@ -18112,7 +18253,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>2025/09/16</t>
         </is>
@@ -18135,7 +18276,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
@@ -18158,7 +18299,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
@@ -18181,7 +18322,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>2025/09/19</t>
         </is>
@@ -18204,7 +18345,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
@@ -18227,7 +18368,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>2025/09/23</t>
         </is>
@@ -18250,7 +18391,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
@@ -18273,7 +18414,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>2025/09/25</t>
         </is>
@@ -18296,7 +18437,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>2025/09/26</t>
         </is>
@@ -18319,7 +18460,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>2025/09/29</t>
         </is>
@@ -18342,7 +18483,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
@@ -18358,14 +18499,14 @@
       <c r="D83" s="0" t="n">
         <v>0.99039</v>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>-1.0245%</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>2025/10/09</t>
         </is>
@@ -18388,7 +18529,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>2025/10/10</t>
         </is>
@@ -18411,7 +18552,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>2025/10/13</t>
         </is>
@@ -18434,7 +18575,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
@@ -18457,7 +18598,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
@@ -18480,7 +18621,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>2025/10/16</t>
         </is>
@@ -18503,7 +18644,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>2025/10/17</t>
         </is>
@@ -18526,7 +18667,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
@@ -18549,7 +18690,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>2025/10/21</t>
         </is>
@@ -18572,7 +18713,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>2025/10/22</t>
         </is>
@@ -18595,7 +18736,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>2025/10/23</t>
         </is>
@@ -18618,7 +18759,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>2025/10/24</t>
         </is>
@@ -18641,7 +18782,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>2025/10/27</t>
         </is>
@@ -18664,7 +18805,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>2025/10/28</t>
         </is>
@@ -18687,7 +18828,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
@@ -18710,7 +18851,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
@@ -18733,7 +18874,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>2025/10/31</t>
         </is>
@@ -18756,7 +18897,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>2025/11/03</t>
         </is>
@@ -18779,7 +18920,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
@@ -18802,7 +18943,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>2025/11/05</t>
         </is>
@@ -18825,7 +18966,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>2025/11/06</t>
         </is>
@@ -18848,7 +18989,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>2025/11/07</t>
         </is>
@@ -18871,7 +19012,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>2025/11/10</t>
         </is>
@@ -18894,7 +19035,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>2025/11/11</t>
         </is>
@@ -18917,7 +19058,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
@@ -18940,7 +19081,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
@@ -18963,7 +19104,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>2025/11/14</t>
         </is>
@@ -18986,7 +19127,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>2025/11/17</t>
         </is>
@@ -19009,7 +19150,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="inlineStr">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>2025/11/18</t>
         </is>
@@ -19032,7 +19173,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>2025/11/19</t>
         </is>
@@ -19055,7 +19196,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>2025/11/20</t>
         </is>
@@ -19078,7 +19219,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="inlineStr">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>2025/11/21</t>
         </is>
@@ -19101,7 +19242,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
@@ -19124,7 +19265,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
@@ -19147,7 +19288,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
@@ -19170,7 +19311,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="10" t="inlineStr">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
@@ -19193,7 +19334,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
@@ -19216,7 +19357,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="10" t="inlineStr">
+      <c r="A121" s="11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
@@ -19239,7 +19380,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
@@ -19262,7 +19403,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
@@ -19285,26 +19426,57 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
+      <c r="A124" s="12" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0.9964499999999999</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>-0.4349%</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>0.98928</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-1.1394%</t>
-        </is>
+      <c r="B124" s="0" t="n">
+        <v>0.99694</v>
+      </c>
+      <c r="C124" s="0" t="n"/>
+      <c r="D124" s="0" t="n">
+        <v>0.98978</v>
+      </c>
+      <c r="E124" s="0" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="n">
+        <v>0.99694</v>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>0.98978</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="n">
+        <v>0.99694</v>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>0.98978</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.99694</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.98978</v>
       </c>
     </row>
   </sheetData>
@@ -19320,13 +19492,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F124"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="14.8888888888889" customWidth="1" style="6" min="2" max="2"/>
-    <col width="14.8888888888889" customWidth="1" style="7" min="3" max="3"/>
-    <col width="14.8888888888889" customWidth="1" style="1" min="4" max="5"/>
-    <col width="14.1111111111111" customWidth="1" style="1" min="6" max="6"/>
+    <col width="14.8916666666667" customWidth="1" style="7" min="2" max="2"/>
+    <col width="14.8916666666667" customWidth="1" style="8" min="3" max="3"/>
+    <col width="14.8916666666667" customWidth="1" style="1" min="4" max="5"/>
+    <col width="14.1083333333333" customWidth="1" style="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19357,7 +19529,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -19365,7 +19537,7 @@
       <c r="B2" s="0" t="n">
         <v>0.99988</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>-0.0124%</t>
         </is>
@@ -19380,7 +19552,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -19403,7 +19575,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -19426,7 +19598,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -19449,7 +19621,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -19472,7 +19644,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -19495,7 +19667,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -19518,7 +19690,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -19541,7 +19713,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -19564,7 +19736,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -19587,7 +19759,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -19610,7 +19782,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -19633,7 +19805,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -19656,7 +19828,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -19679,7 +19851,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -19702,7 +19874,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -19725,7 +19897,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -19748,7 +19920,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -19771,7 +19943,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -19794,7 +19966,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -19817,7 +19989,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -19840,7 +20012,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
@@ -19863,7 +20035,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2025/07/09</t>
         </is>
@@ -19886,7 +20058,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
@@ -19909,7 +20081,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2025/07/11</t>
         </is>
@@ -19932,7 +20104,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2025/07/14</t>
         </is>
@@ -19955,7 +20127,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
@@ -19978,7 +20150,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2025/07/16</t>
         </is>
@@ -20001,7 +20173,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2025/07/17</t>
         </is>
@@ -20024,7 +20196,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
@@ -20047,7 +20219,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2025/07/21</t>
         </is>
@@ -20070,7 +20242,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2025/07/22</t>
         </is>
@@ -20093,7 +20265,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2025/07/23</t>
         </is>
@@ -20116,7 +20288,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
@@ -20139,7 +20311,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2025/07/25</t>
         </is>
@@ -20162,7 +20334,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
@@ -20185,7 +20357,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
@@ -20208,7 +20380,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2025/07/30</t>
         </is>
@@ -20231,7 +20403,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2025/07/31</t>
         </is>
@@ -20254,7 +20426,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2025/08/01</t>
         </is>
@@ -20277,7 +20449,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2025/08/04</t>
         </is>
@@ -20300,7 +20472,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2025/08/05</t>
         </is>
@@ -20323,7 +20495,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2025/08/06</t>
         </is>
@@ -20346,7 +20518,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
@@ -20369,7 +20541,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2025/08/08</t>
         </is>
@@ -20392,7 +20564,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2025/08/11</t>
         </is>
@@ -20415,7 +20587,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2025/08/12</t>
         </is>
@@ -20438,7 +20610,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
@@ -20461,7 +20633,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2025/08/14</t>
         </is>
@@ -20484,7 +20656,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2025/08/15</t>
         </is>
@@ -20507,7 +20679,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
@@ -20530,7 +20702,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2025/08/19</t>
         </is>
@@ -20553,7 +20725,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
@@ -20576,7 +20748,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2025/08/21</t>
         </is>
@@ -20599,7 +20771,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
@@ -20622,7 +20794,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
@@ -20645,7 +20817,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2025/08/26</t>
         </is>
@@ -20668,7 +20840,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
@@ -20691,7 +20863,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>2025/08/28</t>
         </is>
@@ -20714,7 +20886,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
@@ -20737,7 +20909,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
@@ -20760,7 +20932,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>2025/09/02</t>
         </is>
@@ -20783,7 +20955,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
@@ -20806,7 +20978,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>2025/09/04</t>
         </is>
@@ -20829,7 +21001,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>2025/09/05</t>
         </is>
@@ -20852,7 +21024,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2025/09/08</t>
         </is>
@@ -20875,7 +21047,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>2025/09/09</t>
         </is>
@@ -20898,7 +21070,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>2025/09/10</t>
         </is>
@@ -20921,7 +21093,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
@@ -20944,7 +21116,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>2025/09/12</t>
         </is>
@@ -20967,7 +21139,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>2025/09/15</t>
         </is>
@@ -20990,7 +21162,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>2025/09/16</t>
         </is>
@@ -21013,7 +21185,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
@@ -21036,7 +21208,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
@@ -21059,7 +21231,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>2025/09/19</t>
         </is>
@@ -21082,7 +21254,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>2025/09/22</t>
         </is>
@@ -21105,7 +21277,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>2025/09/23</t>
         </is>
@@ -21128,7 +21300,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
@@ -21151,7 +21323,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>2025/09/25</t>
         </is>
@@ -21174,7 +21346,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>2025/09/26</t>
         </is>
@@ -21197,7 +21369,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>2025/09/29</t>
         </is>
@@ -21218,10 +21390,10 @@
           <t>-1.0492%</t>
         </is>
       </c>
-      <c r="F82" s="7" t="n"/>
+      <c r="F82" s="8" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
@@ -21237,14 +21409,14 @@
       <c r="D83" s="0" t="n">
         <v>0.99039</v>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>-1.0245%</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>2025/10/09</t>
         </is>
@@ -21267,7 +21439,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>2025/10/10</t>
         </is>
@@ -21290,7 +21462,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>2025/10/13</t>
         </is>
@@ -21313,7 +21485,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>2025/10/14</t>
         </is>
@@ -21336,7 +21508,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
@@ -21359,7 +21531,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>2025/10/16</t>
         </is>
@@ -21382,7 +21554,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>2025/10/17</t>
         </is>
@@ -21405,7 +21577,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
@@ -21428,7 +21600,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>2025/10/21</t>
         </is>
@@ -21451,7 +21623,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>2025/10/22</t>
         </is>
@@ -21474,7 +21646,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>2025/10/23</t>
         </is>
@@ -21497,7 +21669,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>2025/10/24</t>
         </is>
@@ -21520,7 +21692,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>2025/10/27</t>
         </is>
@@ -21543,7 +21715,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>2025/10/28</t>
         </is>
@@ -21566,7 +21738,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
@@ -21589,7 +21761,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
@@ -21612,7 +21784,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>2025/10/31</t>
         </is>
@@ -21635,7 +21807,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>2025/11/03</t>
         </is>
@@ -21658,7 +21830,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
@@ -21681,7 +21853,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>2025/11/05</t>
         </is>
@@ -21704,7 +21876,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>2025/11/06</t>
         </is>
@@ -21727,7 +21899,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>2025/11/07</t>
         </is>
@@ -21750,7 +21922,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>2025/11/10</t>
         </is>
@@ -21773,7 +21945,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>2025/11/11</t>
         </is>
@@ -21796,7 +21968,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
@@ -21819,7 +21991,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
@@ -21842,7 +22014,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>2025/11/14</t>
         </is>
@@ -21865,7 +22037,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>2025/11/17</t>
         </is>
@@ -21888,7 +22060,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="inlineStr">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>2025/11/18</t>
         </is>
@@ -21911,7 +22083,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>2025/11/19</t>
         </is>
@@ -21934,7 +22106,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>2025/11/20</t>
         </is>
@@ -21957,7 +22129,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="inlineStr">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>2025/11/21</t>
         </is>
@@ -21980,7 +22152,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
@@ -22003,7 +22175,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
@@ -22026,7 +22198,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
@@ -22049,7 +22221,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="10" t="inlineStr">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
@@ -22072,7 +22244,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>2025/11/28</t>
         </is>
@@ -22095,7 +22267,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="10" t="inlineStr">
+      <c r="A121" s="11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
@@ -22118,7 +22290,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
@@ -22141,7 +22313,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
@@ -22164,27 +22336,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0.9964499999999999</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>-0.4349%</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>0.98928</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-1.1394%</t>
-        </is>
-      </c>
+      <c r="A124" s="11" t="n"/>
+      <c r="B124" s="0" t="n"/>
+      <c r="C124" s="0" t="n"/>
+      <c r="D124" s="0" t="n"/>
+      <c r="E124" s="0" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F83"/>
